--- a/output/Tables/2019/HIA_per_sex.xlsx
+++ b/output/Tables/2019/HIA_per_sex.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>24484.449</v>
+        <v>20547.913</v>
       </c>
       <c r="D2">
-        <v>22817.462</v>
+        <v>19111.9</v>
       </c>
       <c r="E2">
-        <v>26152.374</v>
+        <v>21984.152</v>
       </c>
       <c r="F2">
-        <v>286576.089</v>
+        <v>254626.304</v>
       </c>
       <c r="G2">
-        <v>275338.354</v>
+        <v>244138.218</v>
       </c>
       <c r="H2">
-        <v>297893.073</v>
+        <v>265055.536</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>38116177736.526</v>
+        <v>33863647733.242</v>
       </c>
       <c r="M2">
-        <v>36611271347.41</v>
+        <v>32470618909.082</v>
       </c>
       <c r="N2">
-        <v>39614613576.173</v>
+        <v>35255007657.1</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>34004.503</v>
+        <v>30808.016</v>
       </c>
       <c r="D3">
-        <v>31528.612</v>
+        <v>28482.051</v>
       </c>
       <c r="E3">
-        <v>36463.26</v>
+        <v>33126.852</v>
       </c>
       <c r="F3">
-        <v>318196.098</v>
+        <v>297702.557</v>
       </c>
       <c r="G3">
-        <v>302440.325</v>
+        <v>282380.031</v>
       </c>
       <c r="H3">
-        <v>333928.733</v>
+        <v>313049.987</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>42316432594.079</v>
+        <v>39591737743.575</v>
       </c>
       <c r="M3">
-        <v>40223152023.432</v>
+        <v>37548228419.785</v>
       </c>
       <c r="N3">
-        <v>44430109220.601</v>
+        <v>41651434315.345</v>
       </c>
     </row>
     <row r="4">
@@ -534,40 +534,40 @@
         </is>
       </c>
       <c r="C4">
-        <v>18755.11</v>
+        <v>15799.45</v>
       </c>
       <c r="D4">
-        <v>17677.265</v>
+        <v>14834.628</v>
       </c>
       <c r="E4">
-        <v>19839.411</v>
+        <v>16763.215</v>
       </c>
       <c r="F4">
-        <v>19050.332</v>
+        <v>23125.797</v>
       </c>
       <c r="G4">
-        <v>18063.621</v>
+        <v>21871.022</v>
       </c>
       <c r="H4">
-        <v>20046.9</v>
+        <v>24391.331</v>
       </c>
       <c r="I4">
-        <v>1044651627.56</v>
+        <v>832477021.9809999</v>
       </c>
       <c r="J4">
-        <v>984478743.471</v>
+        <v>781607506.2</v>
       </c>
       <c r="K4">
-        <v>1105798318.338</v>
+        <v>883946757.697</v>
       </c>
       <c r="L4">
-        <v>2533963256.375</v>
+        <v>3076072198.276</v>
       </c>
       <c r="M4">
-        <v>2402329375.847</v>
+        <v>2908423995.116</v>
       </c>
       <c r="N4">
-        <v>2667165618.303</v>
+        <v>3245063862.841</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>21385.638</v>
+        <v>19467.622</v>
       </c>
       <c r="D5">
-        <v>19921.581</v>
+        <v>18052.193</v>
       </c>
       <c r="E5">
-        <v>22862.907</v>
+        <v>20898.109</v>
       </c>
       <c r="F5">
-        <v>16871.582</v>
+        <v>25519.881</v>
       </c>
       <c r="G5">
-        <v>15758.314</v>
+        <v>23758.592</v>
       </c>
       <c r="H5">
-        <v>18000.867</v>
+        <v>27303.996</v>
       </c>
       <c r="I5">
-        <v>1191126911.948</v>
+        <v>1025846756.341</v>
       </c>
       <c r="J5">
-        <v>1109578093.424</v>
+        <v>951287109.201</v>
       </c>
       <c r="K5">
-        <v>1273622792.283</v>
+        <v>1101338282.634</v>
       </c>
       <c r="L5">
-        <v>2243857317.734</v>
+        <v>3393698516.27</v>
       </c>
       <c r="M5">
-        <v>2096703098.103</v>
+        <v>3160341318.694</v>
       </c>
       <c r="N5">
-        <v>2393290979.011</v>
+        <v>3630333147.798</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>20111.891</v>
+        <v>3562.112</v>
       </c>
       <c r="D6">
-        <v>18890.766</v>
+        <v>3335.743</v>
       </c>
       <c r="E6">
-        <v>21371.229</v>
+        <v>3793.699</v>
       </c>
       <c r="F6">
-        <v>36172.418</v>
+        <v>1908.042</v>
       </c>
       <c r="G6">
-        <v>33581.435</v>
+        <v>1788.346</v>
       </c>
       <c r="H6">
-        <v>38887.626</v>
+        <v>2030.126</v>
       </c>
       <c r="I6">
-        <v>297819851.486</v>
+        <v>104455857.909</v>
       </c>
       <c r="J6">
-        <v>279728702.968</v>
+        <v>97825979.90899999</v>
       </c>
       <c r="K6">
-        <v>316572288.144</v>
+        <v>111251470.866</v>
       </c>
       <c r="L6">
-        <v>4808911216.95</v>
+        <v>253710807.059</v>
       </c>
       <c r="M6">
-        <v>4468372805.113</v>
+        <v>237915617.668</v>
       </c>
       <c r="N6">
-        <v>5170465782.498</v>
+        <v>269886191.605</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>11094.832</v>
+        <v>4633.024</v>
       </c>
       <c r="D7">
-        <v>10217.263</v>
+        <v>4213.481</v>
       </c>
       <c r="E7">
-        <v>12006.833</v>
+        <v>5067.139</v>
       </c>
       <c r="F7">
-        <v>10871.235</v>
+        <v>1949.745</v>
       </c>
       <c r="G7">
-        <v>10044.652</v>
+        <v>1777.946</v>
       </c>
       <c r="H7">
-        <v>11736</v>
+        <v>2127.602</v>
       </c>
       <c r="I7">
-        <v>164272530.614</v>
+        <v>135835395.087</v>
       </c>
       <c r="J7">
-        <v>151323718.527</v>
+        <v>123517148.435</v>
       </c>
       <c r="K7">
-        <v>177764445.538</v>
+        <v>148512581.447</v>
       </c>
       <c r="L7">
-        <v>1445940904.684</v>
+        <v>259368720.025</v>
       </c>
       <c r="M7">
-        <v>1335700899.647</v>
+        <v>236388890.995</v>
       </c>
       <c r="N7">
-        <v>1560893023.579</v>
+        <v>283040556.108</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>3033.772</v>
+        <v>2617.859</v>
       </c>
       <c r="D8">
-        <v>2842.467</v>
+        <v>2458.747</v>
       </c>
       <c r="E8">
-        <v>3230.255</v>
+        <v>2780.611</v>
       </c>
       <c r="F8">
-        <v>6378.004</v>
+        <v>4420.614</v>
       </c>
       <c r="G8">
-        <v>5953.861</v>
+        <v>4147.955</v>
       </c>
       <c r="H8">
-        <v>6813.448</v>
+        <v>4699.773</v>
       </c>
       <c r="I8">
-        <v>228123789.264</v>
+        <v>102611714.082</v>
       </c>
       <c r="J8">
-        <v>213702470.762</v>
+        <v>96373260.8</v>
       </c>
       <c r="K8">
-        <v>242980675.389</v>
+        <v>108992313.652</v>
       </c>
       <c r="L8">
-        <v>848347981.248</v>
+        <v>588032857.289</v>
       </c>
       <c r="M8">
-        <v>792288071.3710001</v>
+        <v>551887523.844</v>
       </c>
       <c r="N8">
-        <v>906109055.098</v>
+        <v>625081890.865</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>3369.667</v>
+        <v>3134.938</v>
       </c>
       <c r="D9">
-        <v>3117.632</v>
+        <v>2906.447</v>
       </c>
       <c r="E9">
-        <v>3627.484</v>
+        <v>3367.952</v>
       </c>
       <c r="F9">
-        <v>6122.598</v>
+        <v>5931.603</v>
       </c>
       <c r="G9">
-        <v>5646.335</v>
+        <v>5465.87</v>
       </c>
       <c r="H9">
-        <v>6616.702</v>
+        <v>6418.932</v>
       </c>
       <c r="I9">
-        <v>253383229.505</v>
+        <v>122887580.546</v>
       </c>
       <c r="J9">
-        <v>234404738.612</v>
+        <v>113912694.711</v>
       </c>
       <c r="K9">
-        <v>272910382.105</v>
+        <v>132068914.799</v>
       </c>
       <c r="L9">
-        <v>814148185.7410001</v>
+        <v>788928980.385</v>
       </c>
       <c r="M9">
-        <v>750956986.883</v>
+        <v>726717673.997</v>
       </c>
       <c r="N9">
-        <v>880323482.737</v>
+        <v>853100129.5319999</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>8521.370000000001</v>
+        <v>6884.182</v>
       </c>
       <c r="D10">
-        <v>7849.49</v>
+        <v>6296.523</v>
       </c>
       <c r="E10">
-        <v>9194.843999999999</v>
+        <v>7471.494</v>
       </c>
       <c r="F10">
-        <v>16970.107</v>
+        <v>7837.034</v>
       </c>
       <c r="G10">
-        <v>15907.561</v>
+        <v>7161.29</v>
       </c>
       <c r="H10">
-        <v>18050.883</v>
+        <v>8530.927</v>
       </c>
       <c r="I10">
-        <v>143464068.021</v>
+        <v>114578582.441</v>
       </c>
       <c r="J10">
-        <v>132237939.045</v>
+        <v>104876102.997</v>
       </c>
       <c r="K10">
-        <v>154774239.906</v>
+        <v>124370726.194</v>
       </c>
       <c r="L10">
-        <v>2257486458.416</v>
+        <v>1042608204.372</v>
       </c>
       <c r="M10">
-        <v>2115441910.31</v>
+        <v>952838508.674</v>
       </c>
       <c r="N10">
-        <v>2400254421.563</v>
+        <v>1134204060.943</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>5411.453</v>
+        <v>4794.516</v>
       </c>
       <c r="D11">
-        <v>4874.931</v>
+        <v>4288.269</v>
       </c>
       <c r="E11">
-        <v>5959.351</v>
+        <v>5313.169</v>
       </c>
       <c r="F11">
-        <v>6281.251</v>
+        <v>5470.952</v>
       </c>
       <c r="G11">
-        <v>5783.642</v>
+        <v>4875.62</v>
       </c>
       <c r="H11">
-        <v>6787.711</v>
+        <v>6076.52</v>
       </c>
       <c r="I11">
-        <v>91142602.098</v>
+        <v>79826867.436</v>
       </c>
       <c r="J11">
-        <v>82086803.12899999</v>
+        <v>71332657.338</v>
       </c>
       <c r="K11">
-        <v>100350602.535</v>
+        <v>88463712.20999999</v>
       </c>
       <c r="L11">
-        <v>835375892.183</v>
+        <v>727632570.345</v>
       </c>
       <c r="M11">
-        <v>769269845.72</v>
+        <v>648161601.539</v>
       </c>
       <c r="N11">
-        <v>902383886.383</v>
+        <v>808070447.498</v>
       </c>
     </row>
     <row r="12">
@@ -918,22 +918,22 @@
         </is>
       </c>
       <c r="C12">
-        <v>88819.649</v>
+        <v>87029.899</v>
       </c>
       <c r="D12">
-        <v>84397.554</v>
+        <v>82473.355</v>
       </c>
       <c r="E12">
-        <v>93304.664</v>
+        <v>91590.943</v>
       </c>
       <c r="F12">
-        <v>30395.587</v>
+        <v>34807.429</v>
       </c>
       <c r="G12">
-        <v>28403.745</v>
+        <v>32554.924</v>
       </c>
       <c r="H12">
-        <v>32470.677</v>
+        <v>37079.47</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -945,13 +945,13 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>4042315771.149</v>
+        <v>4629227609.811</v>
       </c>
       <c r="M12">
-        <v>3777336898.597</v>
+        <v>4328980696.663</v>
       </c>
       <c r="N12">
-        <v>4318768801.896</v>
+        <v>4931196485.388</v>
       </c>
     </row>
     <row r="13">
@@ -966,22 +966,22 @@
         </is>
       </c>
       <c r="C13">
-        <v>37145.571</v>
+        <v>39192.665</v>
       </c>
       <c r="D13">
-        <v>34994.476</v>
+        <v>36784.292</v>
       </c>
       <c r="E13">
-        <v>39306.954</v>
+        <v>41605.166</v>
       </c>
       <c r="F13">
-        <v>10611.26</v>
+        <v>12952.971</v>
       </c>
       <c r="G13">
-        <v>9808.359</v>
+        <v>11963.846</v>
       </c>
       <c r="H13">
-        <v>11445.969</v>
+        <v>13963.441</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -993,13 +993,13 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>1411022480.577</v>
+        <v>1722882156.348</v>
       </c>
       <c r="M13">
-        <v>1304300582.914</v>
+        <v>1590662939.875</v>
       </c>
       <c r="N13">
-        <v>1521190267.857</v>
+        <v>1856625385.425</v>
       </c>
     </row>
   </sheetData>
